--- a/ig/mc-add-link-doc/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-add-link-doc/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:30:52+00:00</t>
+    <t>2023-05-17T07:53:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
